--- a/results/job_matches_2026-10-10.xlsx
+++ b/results/job_matches_2026-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,17 +806,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Requirements Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>ASRC Federal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hialeah, FL, USA USA</t>
+          <t>Silver Hill, MD, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,69 +824,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Oracle, Data Modeling, Power BI</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf219ffd88edd6e</t>
+          <t>https://www.indeed.com/viewjob?jk=c05632d6ec5ee2d7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Requirements Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASRC Federal</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Silver Hill, MD, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05632d6ec5ee2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer II - (Data Engineering)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Credit One Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II - (Data Engineering)</t>
+          <t>Senior Observability Engineer (Splunk / SignalFx) - US Citizen or Green Card only</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Credit One Bank</t>
+          <t>Nextiya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Fairfax, VA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
+          <t>https://www.indeed.com/viewjob?jk=653c3efd16cc3edd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Observability Engineer (Splunk / SignalFx) - US Citizen or Green Card only</t>
+          <t>Database Analysis - Advisor II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nextiya</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fairfax, VA, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,42 +974,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653c3efd16cc3edd</t>
+          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Database Analysis - Advisor II</t>
+          <t>Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>Murray, UT, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
+          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Scale Marketing</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,34 +1104,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691cad96e500ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,34 +1139,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b6ccb1a0a82581</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b6ccb1a0a82581</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
         </is>
       </c>
     </row>
@@ -1366,17 +1366,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sdfsd</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zacki's Culinary Creations</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Byhalia, MS, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Kafka, Oracle, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,59 +1394,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4582166f5e7749</t>
+          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Rosslyn, VA, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Kafka, Oracle, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=451cbb6ba3d7204d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Engineer III</t>
+          <t>AI, Data &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>QualDerm Partners LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,34 +1454,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451cbb6ba3d7204d</t>
+          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f86cef93b901eda</t>
+          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI, Data &amp; Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QualDerm Partners LLC</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
+          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Spark, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,19 +1569,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Careerwithsmita</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=da461adf5af4b648</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>DBA (Databricks)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Spark, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DBA (Databricks)</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Accurate Background, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,42 +1699,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
+          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Accurate Background, Inc.</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
+          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
+          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Masking Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Aurora, CO, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
+          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Azure Cloud Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Aurora, CO, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer II</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>Stratford, CT, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Senior Software Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stratford, CT, USA USA</t>
+          <t>Hoboken, NJ, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineering</t>
+          <t>Automation Engineer - Platform Integration (Contract)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Allied Universal Electronic Monitoring</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,67 +1989,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Automation Engineer - Platform Integration (Contract)</t>
+          <t>Analyst, Data Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Allied Universal Electronic Monitoring</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
+          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ellis Porter</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Ann Arbor, MI, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
+          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analyst, Data Engineer, Firehouse Subs</t>
+          <t>Data &amp; AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>Lisle, IL, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
+          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
+          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python/AWS)</t>
+          <t>Sr. Python Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>GA, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solutions Engineer</t>
+          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lisle, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,34 +2224,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
+          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,34 +2259,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e80b4019d279f1a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Python Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,34 +2294,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
+          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,29 +2329,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Production Engineer - Realtime Products</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Pursuit Aerospace</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI - Software Engineering-Sr Professional I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pursuit Aerospace</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,14 +2409,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
+          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI - Software Engineering-Sr Professional I</t>
+          <t>AI - Software Engineering Advisor I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI - Software Engineering Advisor I</t>
+          <t>Senior Customer Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
+          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Customer Architect</t>
+          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
+          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,67 +2549,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
+          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
+          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
+          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>Joyce University of Nursing and Health Sciences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Draper, UT, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Sony Interactive Entertainment</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,34 +2679,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
+          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sony Interactive Entertainment</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
+          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer ( Contract -Corp to Corp)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AZ TECHNOLOGY</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb8d2fdac54e89</t>
+          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Radinnova</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
+          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Engineer</t>
+          <t>Data Analytics Analyst 4 4PC- 890</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Radinnova</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
+          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analytics Analyst 4 4PC- 890</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Care Access</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
+          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,112 +2899,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>.NET / PostgreSQL Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Care Access</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=54af70793b1dd612</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Joyce University of Nursing and Health Sciences</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Draper, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-10.xlsx
+++ b/results/job_matches_2026-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,25 +596,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and Analytics Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Brookfield, WI, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dc6eea200704fa</t>
+          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect - MS Fabric</t>
+          <t>IT Data Analytics Specialist - Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brookfield, WI, USA USA</t>
+          <t>Westerville, OH, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Oracle, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT Data Analytics Specialist - Data Engineer</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westerville, OH, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Oracle, Data Modeling, Star Schema</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,67 +694,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb9d612ea54d97c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake DBA</t>
+          <t>Software Requirements Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CLOUDSCOUTS SOFTWARE SOLUTIONS LLC</t>
+          <t>ASRC Federal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Silver Hill, MD, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Time Travel, Dimensional Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f220289c65db145a</t>
+          <t>https://www.indeed.com/viewjob?jk=c05632d6ec5ee2d7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb9d612ea54d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Platforms - REMOTE</t>
+          <t>Senior Observability Engineer (Splunk / SignalFx) - US Citizen or Green Card only</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fortified Data</t>
+          <t>Nextiya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Fairfax, VA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,102 +799,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=653c3efd16cc3edd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Requirements Engineer</t>
+          <t>Database Analysis - Advisor II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASRC Federal</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Silver Hill, MD, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05632d6ec5ee2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Murray, UT, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II - (Data Engineering)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Credit One Bank</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Dayton, OH, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6b54828a79f2eaef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Observability Engineer (Splunk / SignalFx) - US Citizen or Green Card only</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nextiya</t>
+          <t>Huntsman Cancer Institute</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fairfax, VA, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,59 +939,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653c3efd16cc3edd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d07fe5896fdd369</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Database Analysis - Advisor II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
+          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
+          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data and AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Murray, UT, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,34 +999,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b6ccb1a0a82581</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Huntsman Cancer Institute</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d07fe5896fdd369</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>. NET Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dayton, OH, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, SQL Server, Kimball, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,67 +1079,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b54828a79f2eaef</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf663ec36e61e57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Neural Network Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
+          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Machine Learning Engineering Sr -</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b6ccb1a0a82581</t>
+          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
+          <t>https://www.indeed.com/viewjob?jk=444d47d7e5ab373f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>. NET Specialist Software Engineering</t>
+          <t>AI, Data &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>QualDerm Partners LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, SQL Server, Kimball, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,19 +1219,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf663ec36e61e57</t>
+          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T prods solutions inc</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472e078ffbc1788b</t>
+          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Davide Dev Technology &amp; Software Solutions LLC</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,19 +1289,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95518c1035c2ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neural Network Architect</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1310,11 +1310,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
+          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineering Sr -</t>
+          <t>DBA (Databricks)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1345,11 +1345,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,67 +1359,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
+          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Accurate Background, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Kafka, Oracle, ELT, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Engineer III</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,67 +1429,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451cbb6ba3d7204d</t>
+          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI, Data &amp; Automation Engineer</t>
+          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>QualDerm Partners LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
+          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Aurora, CO, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,89 +1534,89 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Stratford, CT, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Spark, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Mobile Software Engineer</t>
+          <t>Senior Software Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Careerwithsmita</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Hoboken, NJ, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da461adf5af4b648</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DBA (Databricks)</t>
+          <t>Automation Engineer - Platform Integration (Contract)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Allied Universal Electronic Monitoring</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1625,11 +1625,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,102 +1639,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
+          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Analyst, Data Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Accurate Background, Inc.</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
+          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Ellis Porter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Ann Arbor, MI, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
+          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
+          <t>Data &amp; AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Lisle, IL, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Masking Engineer</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
+          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Aurora, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,67 +1849,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer II</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>Vienna, VA, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
+          <t>https://www.indeed.com/viewjob?jk=61db4c7367fcd28b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stratford, CT, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Pursuit Aerospace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,59 +1954,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Automation Engineer - Platform Integration (Contract)</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Allied Universal Electronic Monitoring</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
+          <t>Senior Customer Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,34 +2014,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
+          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analyst, Data Engineer, Firehouse Subs</t>
+          <t>AI - Software Engineering Advisor I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI - Software Engineering-Sr Professional I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ellis Porter</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
+          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solutions Engineer</t>
+          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lisle, IL, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,77 +2119,77 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
+          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
+          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Python Data Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,67 +2199,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
+          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Joyce University of Nursing and Health Sciences</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Draper, UT, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
+          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sony Interactive Entertainment</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e80b4019d279f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Production Engineer - Realtime Products</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
+          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pursuit Aerospace</t>
+          <t>Radinnova</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,32 +2374,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
+          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI - Software Engineering-Sr Professional I</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,67 +2409,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI - Software Engineering Advisor I</t>
+          <t>Data Analytics Analyst 4 4PC- 890</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
+          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Customer Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>Care Access</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2478,426 +2478,6 @@
         </is>
       </c>
       <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Boise, ID, USA USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Bitsight</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Sr Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>The Hershey Company</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Dallas, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Joyce University of Nursing and Health Sciences</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Draper, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Sony Interactive Entertainment</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Sr. DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Bitsight</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Microsoft Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Radinnova</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Data Analytics Analyst 4 4PC- 890</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>4P Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Care Access</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=54af70793b1dd612</t>
         </is>

--- a/results/job_matches_2026-10-10.xlsx
+++ b/results/job_matches_2026-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,165 +456,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Databricks Administrator / Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fea8871f48cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=580064bd4b42e559</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Requirements Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>ASRC Federal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Silver Hill, MD, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1716679382a11</t>
+          <t>https://www.indeed.com/viewjob?jk=c05632d6ec5ee2d7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Administrator / Platform Engineer</t>
+          <t>Database Analysis - Advisor II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580064bd4b42e559</t>
+          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Enterprise Architecture</t>
+          <t>Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Murray, UT, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caff522a25e0d7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect - MS Fabric</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Huntsman Cancer Institute</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brookfield, WI, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,207 +624,207 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d07fe5896fdd369</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Data Analytics Specialist - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westerville, OH, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Oracle, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
+          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb9d612ea54d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Requirements Engineer</t>
+          <t>. NET Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASRC Federal</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Silver Hill, MD, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, SQL Server, Kimball, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05632d6ec5ee2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf663ec36e61e57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=28e4964b9a08b633</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Observability Engineer (Splunk / SignalFx) - US Citizen or Green Card only</t>
+          <t>Senior Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nextiya</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fairfax, VA, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653c3efd16cc3edd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Analysis - Advisor II</t>
+          <t>Neural Network Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
+          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data and AI Platform Engineer</t>
+          <t>Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Murray, UT, USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
+          <t>https://www.indeed.com/viewjob?jk=444d47d7e5ab373f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI, Data &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>QualDerm Partners LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b54828a79f2eaef</t>
+          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Huntsman Cancer Institute</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,102 +939,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d07fe5896fdd369</t>
+          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBA (Databricks)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
+          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Accurate Background, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b6ccb1a0a82581</t>
+          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,67 +1044,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
+          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>. NET Specialist Software Engineering</t>
+          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, SQL Server, Kimball, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf663ec36e61e57</t>
+          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Neural Network Architect</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
+          <t>https://www.indeed.com/viewjob?jk=85220dfd201ee108</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineering Sr -</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
+          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Engineer III</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Stratford, CT, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444d47d7e5ab373f</t>
+          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI, Data &amp; Automation Engineer</t>
+          <t>Senior Software Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QualDerm Partners LLC</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Hoboken, NJ, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,19 +1219,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Automation Engineer - Platform Integration (Contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Allied Universal Electronic Monitoring</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,207 +1254,207 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ellis Porter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Ann Arbor, MI, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DBA (Databricks)</t>
+          <t>Data &amp; AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Lisle, IL, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Accurate Background, Inc.</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
+          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
+          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,67 +1464,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Masking Engineer</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>AI - Software Engineering Advisor I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aurora, CO, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,137 +1534,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>AI - Software Engineering-Sr Professional I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stratford, CT, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineering</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Automation Engineer - Platform Integration (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allied Universal Electronic Monitoring</t>
+          <t>Joyce University of Nursing and Health Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Draper, UT, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
+          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sony Interactive Entertainment</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,67 +1674,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
+          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analyst, Data Engineer, Firehouse Subs</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
+          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ellis Porter</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
+          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solutions Engineer</t>
+          <t>Data Analytics Analyst 4 4PC- 890</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lisle, IL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
+          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Care Access</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1813,671 +1813,6 @@
         </is>
       </c>
       <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Application Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Navy Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Vienna, VA, USA USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61db4c7367fcd28b</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Pursuit Aerospace</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Production Engineer - Realtime Products</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Customer Architect</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Harness</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI - Software Engineering Advisor I</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI - Software Engineering-Sr Professional I</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Bitsight</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sr Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>The Hershey Company</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dallas, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Joyce University of Nursing and Health Sciences</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Draper, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Sony Interactive Entertainment</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Sr. DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Bitsight</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Microsoft Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Radinnova</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Analytics Analyst 4 4PC- 890</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>4P Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Care Access</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=54af70793b1dd612</t>
         </is>

--- a/results/job_matches_2026-10-10.xlsx
+++ b/results/job_matches_2026-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,52 +526,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Analysis - Advisor II</t>
+          <t>Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, USA USA</t>
+          <t>Murray, UT, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
+          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data and AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Murray, UT, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
+          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huntsman Cancer Institute</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,42 +614,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d07fe5896fdd369</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, ECS, RDS, Spark, PySpark, MongoDB, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edbd750eb639cae5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,67 +694,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
+          <t>https://www.indeed.com/viewjob?jk=444d47d7e5ab373f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>. NET Specialist Software Engineering</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Accurate Background, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, SQL Server, Kimball, Splunk, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf663ec36e61e57</t>
+          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e4964b9a08b633</t>
+          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare)</t>
+          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,49 +799,49 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
+          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Neural Network Architect</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Stratford, CT, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle, dbt</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
+          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Engineer III</t>
+          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -855,11 +855,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, dbt, Tableau, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,137 +869,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444d47d7e5ab373f</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI, Data &amp; Automation Engineer</t>
+          <t>Data &amp; AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QualDerm Partners LLC</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Lisle, IL, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
+          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Ellis Porter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Ann Arbor, MI, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DBA (Databricks)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b5129b0db8c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Accurate Background, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e62637ed2b2976</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138af48c8d1cab20</t>
+          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Test Data Management / Test Data Engineer/Test Data Architect</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,102 +1079,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938aa39b54658ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Masking Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sony Interactive Entertainment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85220dfd201ee108</t>
+          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Masking Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Joyce University of Nursing and Health Sciences</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Draper, UT, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
+          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stratford, CT, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,637 +1184,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineering</t>
+          <t>Data Analytics Analyst 4 4PC- 890</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Automation Engineer - Platform Integration (Contract)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Allied Universal Electronic Monitoring</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, USA USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Athena, RDS, Snowflake, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Ellis Porter</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, USA USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Dimensional Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd38bdae65c89193</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Molex</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lisle, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Production Engineer - Realtime Products</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc6fea09f662910</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AI - Software Engineering Advisor I</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI - Software Engineering-Sr Professional I</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bitsight</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dc289f40cfcbe1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Joyce University of Nursing and Health Sciences</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Draper, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c42098f2146dcb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sony Interactive Entertainment</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=134d5ae79492a313</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr. DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Scala, ELT, CI/CD, Terraform, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d61188ba482a520</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Bitsight</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bfdf9a7912c1da9</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data Analytics Analyst 4 4PC- 890</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4P Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ETL, ELT, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Care Access</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54af70793b1dd612</t>
         </is>
       </c>
     </row>
